--- a/data/recalls.xlsx
+++ b/data/recalls.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,6 +492,70 @@
           <t>Notes</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FSANZ (AU)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Food recalls remove unsafe food from sale to protect consumers. Food can be recalled for a range of reasons, including p</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Food recalls remove unsafe food from sale to protect consumers. Food can be recalled for a range of reasons, including product contamination, undeclared allergens and labelling errors. When a recall happens, FSANZ works with food businesses and regulators to coordinate the response and inform consum</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Food recalls remove unsafe food from sale to protect consumers. Food can be recalled for a range of reasons, including product contamination, undeclared allergens and labelling errors. When a recall h</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Food recalls remove unsafe food from sale to protect consumers. Food can be recalled for a range of reasons, including product contamination, undeclared allergens and labelling errors. When a recall happens, FSANZ works with food businesses and regulators to coordinate the response and inform consumers. Add block Australian food recall alerts View all 334 recalls Coffee Works - Various Chocolate P</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Recall</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Oceania</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://www.foodstandards.gov.au/food-recalls/recalls</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/recalls.xlsx
+++ b/data/recalls.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recalls" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NEWS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pending" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NEWS" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,12 +31,18 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -50,9 +57,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -647,7 +655,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Southern Alp Sprouts Alfalfa &amp; Onion Sprouts 120g (Batch J197, J199; BB 21/04/2026 &amp; 23/04/2026); Pams Onion Sprouts Combo 120g (Batch J199; BB 23/04/2026)</t>
+          <t>Southern Alp Sprouts Alfalfa &amp; Onion Sprouts 120g (Batch J197, J199); Pams Onion Sprouts Combo 120g (Batch J199)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1181,7 +1189,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chocolate bars with pistachios / Pistachio bites (Barre de chocolat aux pistaches, Bouchées aux pistaches)</t>
+          <t>Chocolate bars with pistachios / Pistachio bites</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -14023,41 +14031,137 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:P1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Pathogen</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Region</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Outbreak</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>ScrapedAt</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Published (UTC)</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Pathogen</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Retrieved (UTC)</t>
         </is>
